--- a/artfynd/A 61224-2024 artfynd.xlsx
+++ b/artfynd/A 61224-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302707</v>
+        <v>122302710</v>
       </c>
       <c r="B2" t="n">
         <v>78645</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455876</v>
+        <v>455835</v>
       </c>
       <c r="R2" t="n">
-        <v>6812238</v>
+        <v>6812283</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302712</v>
+        <v>122302708</v>
       </c>
       <c r="B3" t="n">
         <v>78645</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455812</v>
+        <v>455856</v>
       </c>
       <c r="R3" t="n">
-        <v>6812304</v>
+        <v>6812249</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302539</v>
+        <v>122302699</v>
       </c>
       <c r="B4" t="n">
-        <v>79263</v>
+        <v>78645</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455818</v>
+        <v>455957</v>
       </c>
       <c r="R4" t="n">
-        <v>6812302</v>
+        <v>6812268</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302601</v>
+        <v>122302551</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
+        <v>78679</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455785</v>
+        <v>455816</v>
       </c>
       <c r="R5" t="n">
-        <v>6812291</v>
+        <v>6812302</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302704</v>
+        <v>122302700</v>
       </c>
       <c r="B6" t="n">
         <v>78645</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455926</v>
+        <v>455975</v>
       </c>
       <c r="R6" t="n">
-        <v>6812197</v>
+        <v>6812246</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302703</v>
+        <v>122302701</v>
       </c>
       <c r="B7" t="n">
         <v>78645</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455925</v>
+        <v>455958</v>
       </c>
       <c r="R7" t="n">
-        <v>6812180</v>
+        <v>6812214</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302713</v>
+        <v>122302706</v>
       </c>
       <c r="B8" t="n">
         <v>78645</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455813</v>
+        <v>455915</v>
       </c>
       <c r="R8" t="n">
-        <v>6812305</v>
+        <v>6812217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302714</v>
+        <v>122302704</v>
       </c>
       <c r="B9" t="n">
         <v>78645</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455809</v>
+        <v>455926</v>
       </c>
       <c r="R9" t="n">
-        <v>6812302</v>
+        <v>6812197</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302602</v>
+        <v>122302580</v>
       </c>
       <c r="B10" t="n">
-        <v>78645</v>
+        <v>78382</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455759</v>
+        <v>455866</v>
       </c>
       <c r="R10" t="n">
-        <v>6812303</v>
+        <v>6812243</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302581</v>
+        <v>122302707</v>
       </c>
       <c r="B11" t="n">
-        <v>78382</v>
+        <v>78645</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455818</v>
+        <v>455876</v>
       </c>
       <c r="R11" t="n">
-        <v>6812302</v>
+        <v>6812238</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302580</v>
+        <v>122302713</v>
       </c>
       <c r="B12" t="n">
-        <v>78382</v>
+        <v>78645</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455866</v>
+        <v>455813</v>
       </c>
       <c r="R12" t="n">
-        <v>6812243</v>
+        <v>6812305</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302711</v>
+        <v>122302705</v>
       </c>
       <c r="B13" t="n">
         <v>78645</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455814</v>
+        <v>455920</v>
       </c>
       <c r="R13" t="n">
-        <v>6812303</v>
+        <v>6812215</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302706</v>
+        <v>122302711</v>
       </c>
       <c r="B14" t="n">
         <v>78645</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455915</v>
+        <v>455814</v>
       </c>
       <c r="R14" t="n">
-        <v>6812217</v>
+        <v>6812303</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302710</v>
+        <v>122302712</v>
       </c>
       <c r="B15" t="n">
         <v>78645</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455835</v>
+        <v>455812</v>
       </c>
       <c r="R15" t="n">
-        <v>6812283</v>
+        <v>6812304</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302699</v>
+        <v>122302581</v>
       </c>
       <c r="B16" t="n">
-        <v>78645</v>
+        <v>78382</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455957</v>
+        <v>455818</v>
       </c>
       <c r="R16" t="n">
-        <v>6812268</v>
+        <v>6812302</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302705</v>
+        <v>122302702</v>
       </c>
       <c r="B17" t="n">
         <v>78645</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455920</v>
+        <v>455951</v>
       </c>
       <c r="R17" t="n">
-        <v>6812215</v>
+        <v>6812205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302708</v>
+        <v>122302601</v>
       </c>
       <c r="B18" t="n">
         <v>78645</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455856</v>
+        <v>455785</v>
       </c>
       <c r="R18" t="n">
-        <v>6812249</v>
+        <v>6812291</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302701</v>
+        <v>122302703</v>
       </c>
       <c r="B19" t="n">
         <v>78645</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455958</v>
+        <v>455925</v>
       </c>
       <c r="R19" t="n">
-        <v>6812214</v>
+        <v>6812180</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302709</v>
+        <v>122302714</v>
       </c>
       <c r="B20" t="n">
         <v>78645</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455848</v>
+        <v>455809</v>
       </c>
       <c r="R20" t="n">
-        <v>6812261</v>
+        <v>6812302</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302700</v>
+        <v>122302582</v>
       </c>
       <c r="B22" t="n">
-        <v>78645</v>
+        <v>78382</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455975</v>
+        <v>455811</v>
       </c>
       <c r="R22" t="n">
-        <v>6812246</v>
+        <v>6812306</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302582</v>
+        <v>122302602</v>
       </c>
       <c r="B23" t="n">
-        <v>78382</v>
+        <v>78645</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455811</v>
+        <v>455759</v>
       </c>
       <c r="R23" t="n">
-        <v>6812306</v>
+        <v>6812303</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302551</v>
+        <v>122302709</v>
       </c>
       <c r="B24" t="n">
-        <v>78679</v>
+        <v>78645</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455816</v>
+        <v>455848</v>
       </c>
       <c r="R24" t="n">
-        <v>6812302</v>
+        <v>6812261</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302702</v>
+        <v>122302539</v>
       </c>
       <c r="B25" t="n">
-        <v>78645</v>
+        <v>79263</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455951</v>
+        <v>455818</v>
       </c>
       <c r="R25" t="n">
-        <v>6812205</v>
+        <v>6812302</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 61224-2024 artfynd.xlsx
+++ b/artfynd/A 61224-2024 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302706</v>
+        <v>122302580</v>
       </c>
       <c r="B8" t="n">
-        <v>78645</v>
+        <v>78382</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455915</v>
+        <v>455866</v>
       </c>
       <c r="R8" t="n">
-        <v>6812217</v>
+        <v>6812243</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302704</v>
+        <v>122302706</v>
       </c>
       <c r="B9" t="n">
         <v>78645</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455926</v>
+        <v>455915</v>
       </c>
       <c r="R9" t="n">
-        <v>6812197</v>
+        <v>6812217</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302580</v>
+        <v>122302704</v>
       </c>
       <c r="B10" t="n">
-        <v>78382</v>
+        <v>78645</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455866</v>
+        <v>455926</v>
       </c>
       <c r="R10" t="n">
-        <v>6812243</v>
+        <v>6812197</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302705</v>
+        <v>122302581</v>
       </c>
       <c r="B13" t="n">
-        <v>78645</v>
+        <v>78382</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455920</v>
+        <v>455818</v>
       </c>
       <c r="R13" t="n">
-        <v>6812215</v>
+        <v>6812302</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302711</v>
+        <v>122302705</v>
       </c>
       <c r="B14" t="n">
         <v>78645</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455814</v>
+        <v>455920</v>
       </c>
       <c r="R14" t="n">
-        <v>6812303</v>
+        <v>6812215</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302712</v>
+        <v>122302711</v>
       </c>
       <c r="B15" t="n">
         <v>78645</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455812</v>
+        <v>455814</v>
       </c>
       <c r="R15" t="n">
-        <v>6812304</v>
+        <v>6812303</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302581</v>
+        <v>122302712</v>
       </c>
       <c r="B16" t="n">
-        <v>78382</v>
+        <v>78645</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455818</v>
+        <v>455812</v>
       </c>
       <c r="R16" t="n">
-        <v>6812302</v>
+        <v>6812304</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 61224-2024 artfynd.xlsx
+++ b/artfynd/A 61224-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302710</v>
+        <v>122302702</v>
       </c>
       <c r="B2" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455835</v>
+        <v>455951</v>
       </c>
       <c r="R2" t="n">
-        <v>6812283</v>
+        <v>6812205</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302708</v>
+        <v>122302539</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>79264</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455856</v>
+        <v>455818</v>
       </c>
       <c r="R3" t="n">
-        <v>6812249</v>
+        <v>6812302</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302699</v>
+        <v>122302711</v>
       </c>
       <c r="B4" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455957</v>
+        <v>455814</v>
       </c>
       <c r="R4" t="n">
-        <v>6812268</v>
+        <v>6812303</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302551</v>
+        <v>122302701</v>
       </c>
       <c r="B5" t="n">
-        <v>78679</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455816</v>
+        <v>455958</v>
       </c>
       <c r="R5" t="n">
-        <v>6812302</v>
+        <v>6812214</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302700</v>
+        <v>122302714</v>
       </c>
       <c r="B6" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455975</v>
+        <v>455809</v>
       </c>
       <c r="R6" t="n">
-        <v>6812246</v>
+        <v>6812302</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302701</v>
+        <v>122302704</v>
       </c>
       <c r="B7" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455958</v>
+        <v>455926</v>
       </c>
       <c r="R7" t="n">
-        <v>6812214</v>
+        <v>6812197</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302580</v>
+        <v>122302706</v>
       </c>
       <c r="B8" t="n">
-        <v>78382</v>
+        <v>78646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455866</v>
+        <v>455915</v>
       </c>
       <c r="R8" t="n">
-        <v>6812243</v>
+        <v>6812217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302706</v>
+        <v>122302708</v>
       </c>
       <c r="B9" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455915</v>
+        <v>455856</v>
       </c>
       <c r="R9" t="n">
-        <v>6812217</v>
+        <v>6812249</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302704</v>
+        <v>122302601</v>
       </c>
       <c r="B10" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455926</v>
+        <v>455785</v>
       </c>
       <c r="R10" t="n">
-        <v>6812197</v>
+        <v>6812291</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302707</v>
+        <v>122302700</v>
       </c>
       <c r="B11" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455876</v>
+        <v>455975</v>
       </c>
       <c r="R11" t="n">
-        <v>6812238</v>
+        <v>6812246</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302713</v>
+        <v>122302699</v>
       </c>
       <c r="B12" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455813</v>
+        <v>455957</v>
       </c>
       <c r="R12" t="n">
-        <v>6812305</v>
+        <v>6812268</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
         <v>122302581</v>
       </c>
       <c r="B13" t="n">
-        <v>78382</v>
+        <v>78383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302705</v>
+        <v>122302712</v>
       </c>
       <c r="B14" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455920</v>
+        <v>455812</v>
       </c>
       <c r="R14" t="n">
-        <v>6812215</v>
+        <v>6812304</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302711</v>
+        <v>122302580</v>
       </c>
       <c r="B15" t="n">
-        <v>78645</v>
+        <v>78383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455814</v>
+        <v>455866</v>
       </c>
       <c r="R15" t="n">
-        <v>6812303</v>
+        <v>6812243</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302712</v>
+        <v>122302705</v>
       </c>
       <c r="B16" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455812</v>
+        <v>455920</v>
       </c>
       <c r="R16" t="n">
-        <v>6812304</v>
+        <v>6812215</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302702</v>
+        <v>122302707</v>
       </c>
       <c r="B17" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455951</v>
+        <v>455876</v>
       </c>
       <c r="R17" t="n">
-        <v>6812205</v>
+        <v>6812238</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302601</v>
+        <v>122302710</v>
       </c>
       <c r="B18" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455785</v>
+        <v>455835</v>
       </c>
       <c r="R18" t="n">
-        <v>6812291</v>
+        <v>6812283</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302703</v>
+        <v>122302582</v>
       </c>
       <c r="B19" t="n">
-        <v>78645</v>
+        <v>78383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455925</v>
+        <v>455811</v>
       </c>
       <c r="R19" t="n">
-        <v>6812180</v>
+        <v>6812306</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302714</v>
+        <v>122302715</v>
       </c>
       <c r="B20" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455809</v>
+        <v>455785</v>
       </c>
       <c r="R20" t="n">
-        <v>6812302</v>
+        <v>6812284</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302715</v>
+        <v>122302602</v>
       </c>
       <c r="B21" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455785</v>
+        <v>455759</v>
       </c>
       <c r="R21" t="n">
-        <v>6812284</v>
+        <v>6812303</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302582</v>
+        <v>122302551</v>
       </c>
       <c r="B22" t="n">
-        <v>78382</v>
+        <v>78680</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455811</v>
+        <v>455816</v>
       </c>
       <c r="R22" t="n">
-        <v>6812306</v>
+        <v>6812302</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302602</v>
+        <v>122302713</v>
       </c>
       <c r="B23" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455759</v>
+        <v>455813</v>
       </c>
       <c r="R23" t="n">
-        <v>6812303</v>
+        <v>6812305</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302709</v>
+        <v>122302703</v>
       </c>
       <c r="B24" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455848</v>
+        <v>455925</v>
       </c>
       <c r="R24" t="n">
-        <v>6812261</v>
+        <v>6812180</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302539</v>
+        <v>122302709</v>
       </c>
       <c r="B25" t="n">
-        <v>79263</v>
+        <v>78646</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455818</v>
+        <v>455848</v>
       </c>
       <c r="R25" t="n">
-        <v>6812302</v>
+        <v>6812261</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 61224-2024 artfynd.xlsx
+++ b/artfynd/A 61224-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302702</v>
+        <v>122302708</v>
       </c>
       <c r="B2" t="n">
         <v>78646</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455951</v>
+        <v>455856</v>
       </c>
       <c r="R2" t="n">
-        <v>6812205</v>
+        <v>6812249</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302539</v>
+        <v>122302582</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>78383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455818</v>
+        <v>455811</v>
       </c>
       <c r="R3" t="n">
-        <v>6812302</v>
+        <v>6812306</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302711</v>
+        <v>122302601</v>
       </c>
       <c r="B4" t="n">
         <v>78646</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455814</v>
+        <v>455785</v>
       </c>
       <c r="R4" t="n">
-        <v>6812303</v>
+        <v>6812291</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302701</v>
+        <v>122302703</v>
       </c>
       <c r="B5" t="n">
         <v>78646</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455958</v>
+        <v>455925</v>
       </c>
       <c r="R5" t="n">
-        <v>6812214</v>
+        <v>6812180</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302714</v>
+        <v>122302551</v>
       </c>
       <c r="B6" t="n">
-        <v>78646</v>
+        <v>78680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455809</v>
+        <v>455816</v>
       </c>
       <c r="R6" t="n">
         <v>6812302</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302704</v>
+        <v>122302712</v>
       </c>
       <c r="B7" t="n">
         <v>78646</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455926</v>
+        <v>455812</v>
       </c>
       <c r="R7" t="n">
-        <v>6812197</v>
+        <v>6812304</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302706</v>
+        <v>122302602</v>
       </c>
       <c r="B8" t="n">
         <v>78646</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455915</v>
+        <v>455759</v>
       </c>
       <c r="R8" t="n">
-        <v>6812217</v>
+        <v>6812303</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302708</v>
+        <v>122302581</v>
       </c>
       <c r="B9" t="n">
-        <v>78646</v>
+        <v>78383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455856</v>
+        <v>455818</v>
       </c>
       <c r="R9" t="n">
-        <v>6812249</v>
+        <v>6812302</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302601</v>
+        <v>122302714</v>
       </c>
       <c r="B10" t="n">
         <v>78646</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455785</v>
+        <v>455809</v>
       </c>
       <c r="R10" t="n">
-        <v>6812291</v>
+        <v>6812302</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302700</v>
+        <v>122302539</v>
       </c>
       <c r="B11" t="n">
-        <v>78646</v>
+        <v>79264</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455975</v>
+        <v>455818</v>
       </c>
       <c r="R11" t="n">
-        <v>6812246</v>
+        <v>6812302</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302699</v>
+        <v>122302711</v>
       </c>
       <c r="B12" t="n">
         <v>78646</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455957</v>
+        <v>455814</v>
       </c>
       <c r="R12" t="n">
-        <v>6812268</v>
+        <v>6812303</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302581</v>
+        <v>122302704</v>
       </c>
       <c r="B13" t="n">
-        <v>78383</v>
+        <v>78646</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455818</v>
+        <v>455926</v>
       </c>
       <c r="R13" t="n">
-        <v>6812302</v>
+        <v>6812197</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302712</v>
+        <v>122302580</v>
       </c>
       <c r="B14" t="n">
-        <v>78646</v>
+        <v>78383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455812</v>
+        <v>455866</v>
       </c>
       <c r="R14" t="n">
-        <v>6812304</v>
+        <v>6812243</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302580</v>
+        <v>122302699</v>
       </c>
       <c r="B15" t="n">
-        <v>78383</v>
+        <v>78646</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455866</v>
+        <v>455957</v>
       </c>
       <c r="R15" t="n">
-        <v>6812243</v>
+        <v>6812268</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302705</v>
+        <v>122302713</v>
       </c>
       <c r="B16" t="n">
         <v>78646</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455920</v>
+        <v>455813</v>
       </c>
       <c r="R16" t="n">
-        <v>6812215</v>
+        <v>6812305</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302707</v>
+        <v>122302706</v>
       </c>
       <c r="B17" t="n">
         <v>78646</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455876</v>
+        <v>455915</v>
       </c>
       <c r="R17" t="n">
-        <v>6812238</v>
+        <v>6812217</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302582</v>
+        <v>122302700</v>
       </c>
       <c r="B19" t="n">
-        <v>78383</v>
+        <v>78646</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455811</v>
+        <v>455975</v>
       </c>
       <c r="R19" t="n">
-        <v>6812306</v>
+        <v>6812246</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302715</v>
+        <v>122302702</v>
       </c>
       <c r="B20" t="n">
         <v>78646</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455785</v>
+        <v>455951</v>
       </c>
       <c r="R20" t="n">
-        <v>6812284</v>
+        <v>6812205</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302602</v>
+        <v>122302707</v>
       </c>
       <c r="B21" t="n">
         <v>78646</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455759</v>
+        <v>455876</v>
       </c>
       <c r="R21" t="n">
-        <v>6812303</v>
+        <v>6812238</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302551</v>
+        <v>122302705</v>
       </c>
       <c r="B22" t="n">
-        <v>78680</v>
+        <v>78646</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455816</v>
+        <v>455920</v>
       </c>
       <c r="R22" t="n">
-        <v>6812302</v>
+        <v>6812215</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302713</v>
+        <v>122302701</v>
       </c>
       <c r="B23" t="n">
         <v>78646</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455813</v>
+        <v>455958</v>
       </c>
       <c r="R23" t="n">
-        <v>6812305</v>
+        <v>6812214</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302703</v>
+        <v>122302709</v>
       </c>
       <c r="B24" t="n">
         <v>78646</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455925</v>
+        <v>455848</v>
       </c>
       <c r="R24" t="n">
-        <v>6812180</v>
+        <v>6812261</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302709</v>
+        <v>122302715</v>
       </c>
       <c r="B25" t="n">
         <v>78646</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455848</v>
+        <v>455785</v>
       </c>
       <c r="R25" t="n">
-        <v>6812261</v>
+        <v>6812284</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 61224-2024 artfynd.xlsx
+++ b/artfynd/A 61224-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302708</v>
+        <v>122302602</v>
       </c>
       <c r="B2" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455856</v>
+        <v>455759</v>
       </c>
       <c r="R2" t="n">
-        <v>6812249</v>
+        <v>6812303</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302582</v>
+        <v>122302703</v>
       </c>
       <c r="B3" t="n">
-        <v>78383</v>
+        <v>78651</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455811</v>
+        <v>455925</v>
       </c>
       <c r="R3" t="n">
-        <v>6812306</v>
+        <v>6812180</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302601</v>
+        <v>122302551</v>
       </c>
       <c r="B4" t="n">
-        <v>78646</v>
+        <v>78685</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455785</v>
+        <v>455816</v>
       </c>
       <c r="R4" t="n">
-        <v>6812291</v>
+        <v>6812302</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302703</v>
+        <v>122302707</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455925</v>
+        <v>455876</v>
       </c>
       <c r="R5" t="n">
-        <v>6812180</v>
+        <v>6812238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302551</v>
+        <v>122302713</v>
       </c>
       <c r="B6" t="n">
-        <v>78680</v>
+        <v>78651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455816</v>
+        <v>455813</v>
       </c>
       <c r="R6" t="n">
-        <v>6812302</v>
+        <v>6812305</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302712</v>
+        <v>122302704</v>
       </c>
       <c r="B7" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455812</v>
+        <v>455926</v>
       </c>
       <c r="R7" t="n">
-        <v>6812304</v>
+        <v>6812197</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302602</v>
+        <v>122302715</v>
       </c>
       <c r="B8" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455759</v>
+        <v>455785</v>
       </c>
       <c r="R8" t="n">
-        <v>6812303</v>
+        <v>6812284</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302581</v>
+        <v>122302712</v>
       </c>
       <c r="B9" t="n">
-        <v>78383</v>
+        <v>78651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455818</v>
+        <v>455812</v>
       </c>
       <c r="R9" t="n">
-        <v>6812302</v>
+        <v>6812304</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302714</v>
+        <v>122302711</v>
       </c>
       <c r="B10" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455809</v>
+        <v>455814</v>
       </c>
       <c r="R10" t="n">
-        <v>6812302</v>
+        <v>6812303</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302539</v>
+        <v>122302710</v>
       </c>
       <c r="B11" t="n">
-        <v>79264</v>
+        <v>78651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455818</v>
+        <v>455835</v>
       </c>
       <c r="R11" t="n">
-        <v>6812302</v>
+        <v>6812283</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302711</v>
+        <v>122302539</v>
       </c>
       <c r="B12" t="n">
-        <v>78646</v>
+        <v>79269</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455814</v>
+        <v>455818</v>
       </c>
       <c r="R12" t="n">
-        <v>6812303</v>
+        <v>6812302</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302704</v>
+        <v>122302709</v>
       </c>
       <c r="B13" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455926</v>
+        <v>455848</v>
       </c>
       <c r="R13" t="n">
-        <v>6812197</v>
+        <v>6812261</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
         <v>122302580</v>
       </c>
       <c r="B14" t="n">
-        <v>78383</v>
+        <v>78388</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302699</v>
+        <v>122302714</v>
       </c>
       <c r="B15" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455957</v>
+        <v>455809</v>
       </c>
       <c r="R15" t="n">
-        <v>6812268</v>
+        <v>6812302</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302713</v>
+        <v>122302706</v>
       </c>
       <c r="B16" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455813</v>
+        <v>455915</v>
       </c>
       <c r="R16" t="n">
-        <v>6812305</v>
+        <v>6812217</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302706</v>
+        <v>122302701</v>
       </c>
       <c r="B17" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455915</v>
+        <v>455958</v>
       </c>
       <c r="R17" t="n">
-        <v>6812217</v>
+        <v>6812214</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302710</v>
+        <v>122302601</v>
       </c>
       <c r="B18" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455835</v>
+        <v>455785</v>
       </c>
       <c r="R18" t="n">
-        <v>6812283</v>
+        <v>6812291</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302700</v>
+        <v>122302582</v>
       </c>
       <c r="B19" t="n">
-        <v>78646</v>
+        <v>78388</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455975</v>
+        <v>455811</v>
       </c>
       <c r="R19" t="n">
-        <v>6812246</v>
+        <v>6812306</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302702</v>
+        <v>122302705</v>
       </c>
       <c r="B20" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455951</v>
+        <v>455920</v>
       </c>
       <c r="R20" t="n">
-        <v>6812205</v>
+        <v>6812215</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302707</v>
+        <v>122302702</v>
       </c>
       <c r="B21" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455876</v>
+        <v>455951</v>
       </c>
       <c r="R21" t="n">
-        <v>6812238</v>
+        <v>6812205</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302705</v>
+        <v>122302699</v>
       </c>
       <c r="B22" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455920</v>
+        <v>455957</v>
       </c>
       <c r="R22" t="n">
-        <v>6812215</v>
+        <v>6812268</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302701</v>
+        <v>122302581</v>
       </c>
       <c r="B23" t="n">
-        <v>78646</v>
+        <v>78388</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455958</v>
+        <v>455818</v>
       </c>
       <c r="R23" t="n">
-        <v>6812214</v>
+        <v>6812302</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302709</v>
+        <v>122302708</v>
       </c>
       <c r="B24" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455848</v>
+        <v>455856</v>
       </c>
       <c r="R24" t="n">
-        <v>6812261</v>
+        <v>6812249</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302715</v>
+        <v>122302700</v>
       </c>
       <c r="B25" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455785</v>
+        <v>455975</v>
       </c>
       <c r="R25" t="n">
-        <v>6812284</v>
+        <v>6812246</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 61224-2024 artfynd.xlsx
+++ b/artfynd/A 61224-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302602</v>
+        <v>122302708</v>
       </c>
       <c r="B2" t="n">
         <v>78651</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455759</v>
+        <v>455856</v>
       </c>
       <c r="R2" t="n">
-        <v>6812303</v>
+        <v>6812249</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302703</v>
+        <v>122302601</v>
       </c>
       <c r="B3" t="n">
         <v>78651</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455925</v>
+        <v>455785</v>
       </c>
       <c r="R3" t="n">
-        <v>6812180</v>
+        <v>6812291</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302551</v>
+        <v>122302701</v>
       </c>
       <c r="B4" t="n">
-        <v>78685</v>
+        <v>78651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455816</v>
+        <v>455958</v>
       </c>
       <c r="R4" t="n">
-        <v>6812302</v>
+        <v>6812214</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302707</v>
+        <v>122302702</v>
       </c>
       <c r="B5" t="n">
         <v>78651</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455876</v>
+        <v>455951</v>
       </c>
       <c r="R5" t="n">
-        <v>6812238</v>
+        <v>6812205</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302713</v>
+        <v>122302539</v>
       </c>
       <c r="B6" t="n">
-        <v>78651</v>
+        <v>79269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455813</v>
+        <v>455818</v>
       </c>
       <c r="R6" t="n">
-        <v>6812305</v>
+        <v>6812302</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302704</v>
+        <v>122302699</v>
       </c>
       <c r="B7" t="n">
         <v>78651</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455926</v>
+        <v>455957</v>
       </c>
       <c r="R7" t="n">
-        <v>6812197</v>
+        <v>6812268</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302715</v>
+        <v>122302705</v>
       </c>
       <c r="B8" t="n">
         <v>78651</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455785</v>
+        <v>455920</v>
       </c>
       <c r="R8" t="n">
-        <v>6812284</v>
+        <v>6812215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302712</v>
+        <v>122302707</v>
       </c>
       <c r="B9" t="n">
         <v>78651</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455812</v>
+        <v>455876</v>
       </c>
       <c r="R9" t="n">
-        <v>6812304</v>
+        <v>6812238</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302710</v>
+        <v>122302582</v>
       </c>
       <c r="B11" t="n">
-        <v>78651</v>
+        <v>78388</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455835</v>
+        <v>455811</v>
       </c>
       <c r="R11" t="n">
-        <v>6812283</v>
+        <v>6812306</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302539</v>
+        <v>122302700</v>
       </c>
       <c r="B12" t="n">
-        <v>79269</v>
+        <v>78651</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455818</v>
+        <v>455975</v>
       </c>
       <c r="R12" t="n">
-        <v>6812302</v>
+        <v>6812246</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302709</v>
+        <v>122302715</v>
       </c>
       <c r="B13" t="n">
         <v>78651</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455848</v>
+        <v>455785</v>
       </c>
       <c r="R13" t="n">
-        <v>6812261</v>
+        <v>6812284</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302580</v>
+        <v>122302712</v>
       </c>
       <c r="B14" t="n">
-        <v>78388</v>
+        <v>78651</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455866</v>
+        <v>455812</v>
       </c>
       <c r="R14" t="n">
-        <v>6812243</v>
+        <v>6812304</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302714</v>
+        <v>122302706</v>
       </c>
       <c r="B15" t="n">
         <v>78651</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455809</v>
+        <v>455915</v>
       </c>
       <c r="R15" t="n">
-        <v>6812302</v>
+        <v>6812217</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302706</v>
+        <v>122302580</v>
       </c>
       <c r="B16" t="n">
-        <v>78651</v>
+        <v>78388</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455915</v>
+        <v>455866</v>
       </c>
       <c r="R16" t="n">
-        <v>6812217</v>
+        <v>6812243</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302701</v>
+        <v>122302714</v>
       </c>
       <c r="B17" t="n">
         <v>78651</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455958</v>
+        <v>455809</v>
       </c>
       <c r="R17" t="n">
-        <v>6812214</v>
+        <v>6812302</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302601</v>
+        <v>122302703</v>
       </c>
       <c r="B18" t="n">
         <v>78651</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455785</v>
+        <v>455925</v>
       </c>
       <c r="R18" t="n">
-        <v>6812291</v>
+        <v>6812180</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302582</v>
+        <v>122302710</v>
       </c>
       <c r="B19" t="n">
-        <v>78388</v>
+        <v>78651</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455811</v>
+        <v>455835</v>
       </c>
       <c r="R19" t="n">
-        <v>6812306</v>
+        <v>6812283</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302705</v>
+        <v>122302713</v>
       </c>
       <c r="B20" t="n">
         <v>78651</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455920</v>
+        <v>455813</v>
       </c>
       <c r="R20" t="n">
-        <v>6812215</v>
+        <v>6812305</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302702</v>
+        <v>122302709</v>
       </c>
       <c r="B21" t="n">
         <v>78651</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455951</v>
+        <v>455848</v>
       </c>
       <c r="R21" t="n">
-        <v>6812205</v>
+        <v>6812261</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302699</v>
+        <v>122302704</v>
       </c>
       <c r="B22" t="n">
         <v>78651</v>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455957</v>
+        <v>455926</v>
       </c>
       <c r="R22" t="n">
-        <v>6812268</v>
+        <v>6812197</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302581</v>
+        <v>122302602</v>
       </c>
       <c r="B23" t="n">
-        <v>78388</v>
+        <v>78651</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455818</v>
+        <v>455759</v>
       </c>
       <c r="R23" t="n">
-        <v>6812302</v>
+        <v>6812303</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302708</v>
+        <v>122302551</v>
       </c>
       <c r="B24" t="n">
-        <v>78651</v>
+        <v>78685</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455856</v>
+        <v>455816</v>
       </c>
       <c r="R24" t="n">
-        <v>6812249</v>
+        <v>6812302</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302700</v>
+        <v>122302581</v>
       </c>
       <c r="B25" t="n">
-        <v>78651</v>
+        <v>78388</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455975</v>
+        <v>455818</v>
       </c>
       <c r="R25" t="n">
-        <v>6812246</v>
+        <v>6812302</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 61224-2024 artfynd.xlsx
+++ b/artfynd/A 61224-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302601</v>
+        <v>122302702</v>
       </c>
       <c r="B3" t="n">
         <v>78651</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455785</v>
+        <v>455951</v>
       </c>
       <c r="R3" t="n">
-        <v>6812291</v>
+        <v>6812205</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302701</v>
+        <v>122302601</v>
       </c>
       <c r="B4" t="n">
         <v>78651</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455958</v>
+        <v>455785</v>
       </c>
       <c r="R4" t="n">
-        <v>6812214</v>
+        <v>6812291</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302702</v>
+        <v>122302701</v>
       </c>
       <c r="B5" t="n">
         <v>78651</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455951</v>
+        <v>455958</v>
       </c>
       <c r="R5" t="n">
-        <v>6812205</v>
+        <v>6812214</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 61224-2024 artfynd.xlsx
+++ b/artfynd/A 61224-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302708</v>
+        <v>122302706</v>
       </c>
       <c r="B2" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>6425</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455856</v>
+        <v>455915</v>
       </c>
       <c r="R2" t="n">
-        <v>6812249</v>
+        <v>6812217</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302702</v>
+        <v>122302601</v>
       </c>
       <c r="B3" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,11 +790,6 @@
       <c r="E3" t="n">
         <v>6425</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455951</v>
+        <v>455785</v>
       </c>
       <c r="R3" t="n">
-        <v>6812205</v>
+        <v>6812291</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302601</v>
+        <v>122302711</v>
       </c>
       <c r="B4" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,11 +887,6 @@
       <c r="E4" t="n">
         <v>6425</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455785</v>
+        <v>455814</v>
       </c>
       <c r="R4" t="n">
-        <v>6812291</v>
+        <v>6812303</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302701</v>
+        <v>122302713</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -999,11 +984,6 @@
       <c r="E5" t="n">
         <v>6425</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455958</v>
+        <v>455813</v>
       </c>
       <c r="R5" t="n">
-        <v>6812214</v>
+        <v>6812305</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302539</v>
+        <v>122302715</v>
       </c>
       <c r="B6" t="n">
-        <v>79269</v>
+        <v>78652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1079,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455818</v>
+        <v>455785</v>
       </c>
       <c r="R6" t="n">
-        <v>6812302</v>
+        <v>6812284</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302699</v>
+        <v>122302701</v>
       </c>
       <c r="B7" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1203,11 +1178,6 @@
       <c r="E7" t="n">
         <v>6425</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455957</v>
+        <v>455958</v>
       </c>
       <c r="R7" t="n">
-        <v>6812268</v>
+        <v>6812214</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302705</v>
+        <v>122302702</v>
       </c>
       <c r="B8" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,11 +1275,6 @@
       <c r="E8" t="n">
         <v>6425</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455920</v>
+        <v>455951</v>
       </c>
       <c r="R8" t="n">
-        <v>6812215</v>
+        <v>6812205</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302707</v>
+        <v>122302703</v>
       </c>
       <c r="B9" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1407,11 +1372,6 @@
       <c r="E9" t="n">
         <v>6425</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455876</v>
+        <v>455925</v>
       </c>
       <c r="R9" t="n">
-        <v>6812238</v>
+        <v>6812180</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302711</v>
+        <v>122302580</v>
       </c>
       <c r="B10" t="n">
-        <v>78651</v>
+        <v>78389</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1467,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>228912</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455814</v>
+        <v>455866</v>
       </c>
       <c r="R10" t="n">
-        <v>6812303</v>
+        <v>6812243</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302582</v>
+        <v>122302708</v>
       </c>
       <c r="B11" t="n">
-        <v>78388</v>
+        <v>78652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1564,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455811</v>
+        <v>455856</v>
       </c>
       <c r="R11" t="n">
-        <v>6812306</v>
+        <v>6812249</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302700</v>
+        <v>122302704</v>
       </c>
       <c r="B12" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1713,11 +1663,6 @@
       <c r="E12" t="n">
         <v>6425</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455975</v>
+        <v>455926</v>
       </c>
       <c r="R12" t="n">
-        <v>6812246</v>
+        <v>6812197</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302715</v>
+        <v>122302539</v>
       </c>
       <c r="B13" t="n">
-        <v>78651</v>
+        <v>79270</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1758,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6453</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455785</v>
+        <v>455818</v>
       </c>
       <c r="R13" t="n">
-        <v>6812284</v>
+        <v>6812302</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302712</v>
+        <v>122302709</v>
       </c>
       <c r="B14" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1917,11 +1857,6 @@
       <c r="E14" t="n">
         <v>6425</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1939,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455812</v>
+        <v>455848</v>
       </c>
       <c r="R14" t="n">
-        <v>6812304</v>
+        <v>6812261</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302706</v>
+        <v>122302712</v>
       </c>
       <c r="B15" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2019,11 +1954,6 @@
       <c r="E15" t="n">
         <v>6425</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2041,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455915</v>
+        <v>455812</v>
       </c>
       <c r="R15" t="n">
-        <v>6812217</v>
+        <v>6812304</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302580</v>
+        <v>122302602</v>
       </c>
       <c r="B16" t="n">
-        <v>78388</v>
+        <v>78652</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2049,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455866</v>
+        <v>455759</v>
       </c>
       <c r="R16" t="n">
-        <v>6812243</v>
+        <v>6812303</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302714</v>
+        <v>122302705</v>
       </c>
       <c r="B17" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2223,11 +2148,6 @@
       <c r="E17" t="n">
         <v>6425</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2245,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455809</v>
+        <v>455920</v>
       </c>
       <c r="R17" t="n">
-        <v>6812302</v>
+        <v>6812215</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302703</v>
+        <v>122302710</v>
       </c>
       <c r="B18" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2325,11 +2245,6 @@
       <c r="E18" t="n">
         <v>6425</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2347,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455925</v>
+        <v>455835</v>
       </c>
       <c r="R18" t="n">
-        <v>6812180</v>
+        <v>6812283</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302710</v>
+        <v>122302714</v>
       </c>
       <c r="B19" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2427,11 +2342,6 @@
       <c r="E19" t="n">
         <v>6425</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2449,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455835</v>
+        <v>455809</v>
       </c>
       <c r="R19" t="n">
-        <v>6812283</v>
+        <v>6812302</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302713</v>
+        <v>122302699</v>
       </c>
       <c r="B20" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2529,11 +2439,6 @@
       <c r="E20" t="n">
         <v>6425</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2551,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455813</v>
+        <v>455957</v>
       </c>
       <c r="R20" t="n">
-        <v>6812305</v>
+        <v>6812268</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302709</v>
+        <v>122302581</v>
       </c>
       <c r="B21" t="n">
-        <v>78651</v>
+        <v>78389</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2534,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>228912</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455848</v>
+        <v>455818</v>
       </c>
       <c r="R21" t="n">
-        <v>6812261</v>
+        <v>6812302</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302704</v>
+        <v>122302707</v>
       </c>
       <c r="B22" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2733,11 +2633,6 @@
       <c r="E22" t="n">
         <v>6425</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2755,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455926</v>
+        <v>455876</v>
       </c>
       <c r="R22" t="n">
-        <v>6812197</v>
+        <v>6812238</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302602</v>
+        <v>122302700</v>
       </c>
       <c r="B23" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2835,11 +2730,6 @@
       <c r="E23" t="n">
         <v>6425</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2857,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455759</v>
+        <v>455975</v>
       </c>
       <c r="R23" t="n">
-        <v>6812303</v>
+        <v>6812246</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302551</v>
+        <v>122302582</v>
       </c>
       <c r="B24" t="n">
-        <v>78685</v>
+        <v>78389</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2825,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
+        <v>228912</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455816</v>
+        <v>455811</v>
       </c>
       <c r="R24" t="n">
-        <v>6812302</v>
+        <v>6812306</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302581</v>
+        <v>122302551</v>
       </c>
       <c r="B25" t="n">
-        <v>78388</v>
+        <v>78686</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +2922,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>185</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,7 +2941,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455818</v>
+        <v>455816</v>
       </c>
       <c r="R25" t="n">
         <v>6812302</v>

--- a/artfynd/A 61224-2024 artfynd.xlsx
+++ b/artfynd/A 61224-2024 artfynd.xlsx
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302705</v>
+        <v>122302581</v>
       </c>
       <c r="B17" t="n">
-        <v>78652</v>
+        <v>78389</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2146,16 +2146,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455920</v>
+        <v>455818</v>
       </c>
       <c r="R17" t="n">
-        <v>6812215</v>
+        <v>6812302</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302710</v>
+        <v>122302705</v>
       </c>
       <c r="B18" t="n">
         <v>78652</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455835</v>
+        <v>455920</v>
       </c>
       <c r="R18" t="n">
-        <v>6812283</v>
+        <v>6812215</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302714</v>
+        <v>122302710</v>
       </c>
       <c r="B19" t="n">
         <v>78652</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455809</v>
+        <v>455835</v>
       </c>
       <c r="R19" t="n">
-        <v>6812302</v>
+        <v>6812283</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302699</v>
+        <v>122302714</v>
       </c>
       <c r="B20" t="n">
         <v>78652</v>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455957</v>
+        <v>455809</v>
       </c>
       <c r="R20" t="n">
-        <v>6812268</v>
+        <v>6812302</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302581</v>
+        <v>122302699</v>
       </c>
       <c r="B21" t="n">
-        <v>78389</v>
+        <v>78652</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2534,16 +2534,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455818</v>
+        <v>455957</v>
       </c>
       <c r="R21" t="n">
-        <v>6812302</v>
+        <v>6812268</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 61224-2024 artfynd.xlsx
+++ b/artfynd/A 61224-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302706</v>
+        <v>122302703</v>
       </c>
       <c r="B2" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>6425</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455915</v>
+        <v>455925</v>
       </c>
       <c r="R2" t="n">
-        <v>6812217</v>
+        <v>6812180</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302601</v>
+        <v>122302602</v>
       </c>
       <c r="B3" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,6 +795,11 @@
       <c r="E3" t="n">
         <v>6425</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455785</v>
+        <v>455759</v>
       </c>
       <c r="R3" t="n">
-        <v>6812291</v>
+        <v>6812303</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302711</v>
+        <v>122302715</v>
       </c>
       <c r="B4" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -887,6 +897,11 @@
       <c r="E4" t="n">
         <v>6425</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -904,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455814</v>
+        <v>455785</v>
       </c>
       <c r="R4" t="n">
-        <v>6812303</v>
+        <v>6812284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302713</v>
+        <v>122302707</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -984,6 +999,11 @@
       <c r="E5" t="n">
         <v>6425</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1001,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455813</v>
+        <v>455876</v>
       </c>
       <c r="R5" t="n">
-        <v>6812305</v>
+        <v>6812238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302715</v>
+        <v>122302582</v>
       </c>
       <c r="B6" t="n">
-        <v>78652</v>
+        <v>78393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1079,16 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455785</v>
+        <v>455811</v>
       </c>
       <c r="R6" t="n">
-        <v>6812284</v>
+        <v>6812306</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302701</v>
+        <v>122302712</v>
       </c>
       <c r="B7" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1178,6 +1203,11 @@
       <c r="E7" t="n">
         <v>6425</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1195,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455958</v>
+        <v>455812</v>
       </c>
       <c r="R7" t="n">
-        <v>6812214</v>
+        <v>6812304</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302702</v>
+        <v>122302706</v>
       </c>
       <c r="B8" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1275,6 +1305,11 @@
       <c r="E8" t="n">
         <v>6425</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1292,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455951</v>
+        <v>455915</v>
       </c>
       <c r="R8" t="n">
-        <v>6812205</v>
+        <v>6812217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302703</v>
+        <v>122302709</v>
       </c>
       <c r="B9" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1372,6 +1407,11 @@
       <c r="E9" t="n">
         <v>6425</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1389,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455925</v>
+        <v>455848</v>
       </c>
       <c r="R9" t="n">
-        <v>6812180</v>
+        <v>6812261</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302580</v>
+        <v>122302551</v>
       </c>
       <c r="B10" t="n">
-        <v>78389</v>
+        <v>78690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1467,16 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>185</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455866</v>
+        <v>455816</v>
       </c>
       <c r="R10" t="n">
-        <v>6812243</v>
+        <v>6812302</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302708</v>
+        <v>122302702</v>
       </c>
       <c r="B11" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1566,6 +1611,11 @@
       <c r="E11" t="n">
         <v>6425</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1583,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455856</v>
+        <v>455951</v>
       </c>
       <c r="R11" t="n">
-        <v>6812249</v>
+        <v>6812205</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302704</v>
+        <v>122302710</v>
       </c>
       <c r="B12" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1663,6 +1713,11 @@
       <c r="E12" t="n">
         <v>6425</v>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1680,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455926</v>
+        <v>455835</v>
       </c>
       <c r="R12" t="n">
-        <v>6812197</v>
+        <v>6812283</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302539</v>
+        <v>122302700</v>
       </c>
       <c r="B13" t="n">
-        <v>79270</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1758,16 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455818</v>
+        <v>455975</v>
       </c>
       <c r="R13" t="n">
-        <v>6812302</v>
+        <v>6812246</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302709</v>
+        <v>122302713</v>
       </c>
       <c r="B14" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1857,6 +1917,11 @@
       <c r="E14" t="n">
         <v>6425</v>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1874,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455848</v>
+        <v>455813</v>
       </c>
       <c r="R14" t="n">
-        <v>6812261</v>
+        <v>6812305</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302712</v>
+        <v>122302714</v>
       </c>
       <c r="B15" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1954,6 +2019,11 @@
       <c r="E15" t="n">
         <v>6425</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1971,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455812</v>
+        <v>455809</v>
       </c>
       <c r="R15" t="n">
-        <v>6812304</v>
+        <v>6812302</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302602</v>
+        <v>122302704</v>
       </c>
       <c r="B16" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2051,6 +2121,11 @@
       <c r="E16" t="n">
         <v>6425</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2068,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455759</v>
+        <v>455926</v>
       </c>
       <c r="R16" t="n">
-        <v>6812303</v>
+        <v>6812197</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302581</v>
+        <v>122302711</v>
       </c>
       <c r="B17" t="n">
-        <v>78389</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2146,16 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455818</v>
+        <v>455814</v>
       </c>
       <c r="R17" t="n">
-        <v>6812302</v>
+        <v>6812303</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2230,7 +2310,7 @@
         <v>122302705</v>
       </c>
       <c r="B18" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2244,6 +2324,11 @@
       </c>
       <c r="E18" t="n">
         <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2324,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302710</v>
+        <v>122302539</v>
       </c>
       <c r="B19" t="n">
-        <v>78652</v>
+        <v>79274</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2340,16 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455835</v>
+        <v>455818</v>
       </c>
       <c r="R19" t="n">
-        <v>6812283</v>
+        <v>6812302</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302714</v>
+        <v>122302581</v>
       </c>
       <c r="B20" t="n">
-        <v>78652</v>
+        <v>78393</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2437,16 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,7 +2551,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455809</v>
+        <v>455818</v>
       </c>
       <c r="R20" t="n">
         <v>6812302</v>
@@ -2518,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302699</v>
+        <v>122302580</v>
       </c>
       <c r="B21" t="n">
-        <v>78652</v>
+        <v>78393</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2534,16 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455957</v>
+        <v>455866</v>
       </c>
       <c r="R21" t="n">
-        <v>6812268</v>
+        <v>6812243</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302707</v>
+        <v>122302601</v>
       </c>
       <c r="B22" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2633,6 +2733,11 @@
       <c r="E22" t="n">
         <v>6425</v>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2650,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455876</v>
+        <v>455785</v>
       </c>
       <c r="R22" t="n">
-        <v>6812238</v>
+        <v>6812291</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302700</v>
+        <v>122302699</v>
       </c>
       <c r="B23" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2730,6 +2835,11 @@
       <c r="E23" t="n">
         <v>6425</v>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2747,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455975</v>
+        <v>455957</v>
       </c>
       <c r="R23" t="n">
-        <v>6812246</v>
+        <v>6812268</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302582</v>
+        <v>122302701</v>
       </c>
       <c r="B24" t="n">
-        <v>78389</v>
+        <v>78656</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2825,16 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455811</v>
+        <v>455958</v>
       </c>
       <c r="R24" t="n">
-        <v>6812306</v>
+        <v>6812214</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302551</v>
+        <v>122302708</v>
       </c>
       <c r="B25" t="n">
-        <v>78686</v>
+        <v>78656</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2922,16 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455816</v>
+        <v>455856</v>
       </c>
       <c r="R25" t="n">
-        <v>6812302</v>
+        <v>6812249</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 61224-2024 artfynd.xlsx
+++ b/artfynd/A 61224-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302703</v>
+        <v>122302702</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455925</v>
+        <v>455951</v>
       </c>
       <c r="R2" t="n">
-        <v>6812180</v>
+        <v>6812205</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302602</v>
+        <v>122302700</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455759</v>
+        <v>455975</v>
       </c>
       <c r="R3" t="n">
-        <v>6812303</v>
+        <v>6812246</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302715</v>
+        <v>122302703</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455785</v>
+        <v>455925</v>
       </c>
       <c r="R4" t="n">
-        <v>6812284</v>
+        <v>6812180</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302707</v>
+        <v>122302582</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455876</v>
+        <v>455811</v>
       </c>
       <c r="R5" t="n">
-        <v>6812238</v>
+        <v>6812306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302582</v>
+        <v>122302709</v>
       </c>
       <c r="B6" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455811</v>
+        <v>455848</v>
       </c>
       <c r="R6" t="n">
-        <v>6812306</v>
+        <v>6812261</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302712</v>
+        <v>122302714</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455812</v>
+        <v>455809</v>
       </c>
       <c r="R7" t="n">
-        <v>6812304</v>
+        <v>6812302</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302706</v>
+        <v>122302715</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455915</v>
+        <v>455785</v>
       </c>
       <c r="R8" t="n">
-        <v>6812217</v>
+        <v>6812284</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302709</v>
+        <v>122302707</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455848</v>
+        <v>455876</v>
       </c>
       <c r="R9" t="n">
-        <v>6812261</v>
+        <v>6812238</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302551</v>
+        <v>122302710</v>
       </c>
       <c r="B10" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455816</v>
+        <v>455835</v>
       </c>
       <c r="R10" t="n">
-        <v>6812302</v>
+        <v>6812283</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302702</v>
+        <v>122302581</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455951</v>
+        <v>455818</v>
       </c>
       <c r="R11" t="n">
-        <v>6812205</v>
+        <v>6812302</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302710</v>
+        <v>122302601</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455835</v>
+        <v>455785</v>
       </c>
       <c r="R12" t="n">
-        <v>6812283</v>
+        <v>6812291</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302700</v>
+        <v>122302712</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455975</v>
+        <v>455812</v>
       </c>
       <c r="R13" t="n">
-        <v>6812246</v>
+        <v>6812304</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302713</v>
+        <v>122302708</v>
       </c>
       <c r="B14" t="n">
         <v>78656</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455813</v>
+        <v>455856</v>
       </c>
       <c r="R14" t="n">
-        <v>6812305</v>
+        <v>6812249</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302714</v>
+        <v>122302704</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455809</v>
+        <v>455926</v>
       </c>
       <c r="R15" t="n">
-        <v>6812302</v>
+        <v>6812197</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302704</v>
+        <v>122302706</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455926</v>
+        <v>455915</v>
       </c>
       <c r="R16" t="n">
-        <v>6812197</v>
+        <v>6812217</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302711</v>
+        <v>122302539</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455814</v>
+        <v>455818</v>
       </c>
       <c r="R17" t="n">
-        <v>6812303</v>
+        <v>6812302</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302705</v>
+        <v>122302699</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455920</v>
+        <v>455957</v>
       </c>
       <c r="R18" t="n">
-        <v>6812215</v>
+        <v>6812268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302539</v>
+        <v>122302705</v>
       </c>
       <c r="B19" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455818</v>
+        <v>455920</v>
       </c>
       <c r="R19" t="n">
-        <v>6812302</v>
+        <v>6812215</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302581</v>
+        <v>122302711</v>
       </c>
       <c r="B20" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455818</v>
+        <v>455814</v>
       </c>
       <c r="R20" t="n">
-        <v>6812302</v>
+        <v>6812303</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302601</v>
+        <v>122302551</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>78690</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455785</v>
+        <v>455816</v>
       </c>
       <c r="R22" t="n">
-        <v>6812291</v>
+        <v>6812302</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302699</v>
+        <v>122302713</v>
       </c>
       <c r="B23" t="n">
         <v>78656</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455957</v>
+        <v>455813</v>
       </c>
       <c r="R23" t="n">
-        <v>6812268</v>
+        <v>6812305</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302701</v>
+        <v>122302602</v>
       </c>
       <c r="B24" t="n">
         <v>78656</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455958</v>
+        <v>455759</v>
       </c>
       <c r="R24" t="n">
-        <v>6812214</v>
+        <v>6812303</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302708</v>
+        <v>122302701</v>
       </c>
       <c r="B25" t="n">
         <v>78656</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455856</v>
+        <v>455958</v>
       </c>
       <c r="R25" t="n">
-        <v>6812249</v>
+        <v>6812214</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 61224-2024 artfynd.xlsx
+++ b/artfynd/A 61224-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302700</v>
+        <v>122302713</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455975</v>
+        <v>455813</v>
       </c>
       <c r="R3" t="n">
-        <v>6812246</v>
+        <v>6812305</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302703</v>
+        <v>122302708</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455925</v>
+        <v>455856</v>
       </c>
       <c r="R4" t="n">
-        <v>6812180</v>
+        <v>6812249</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302582</v>
+        <v>122302580</v>
       </c>
       <c r="B5" t="n">
         <v>78393</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455811</v>
+        <v>455866</v>
       </c>
       <c r="R5" t="n">
-        <v>6812306</v>
+        <v>6812243</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302709</v>
+        <v>122302706</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455848</v>
+        <v>455915</v>
       </c>
       <c r="R6" t="n">
-        <v>6812261</v>
+        <v>6812217</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302714</v>
+        <v>122302705</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455809</v>
+        <v>455920</v>
       </c>
       <c r="R7" t="n">
-        <v>6812302</v>
+        <v>6812215</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302715</v>
+        <v>122302700</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455785</v>
+        <v>455975</v>
       </c>
       <c r="R8" t="n">
-        <v>6812284</v>
+        <v>6812246</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302707</v>
+        <v>122302704</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455876</v>
+        <v>455926</v>
       </c>
       <c r="R9" t="n">
-        <v>6812238</v>
+        <v>6812197</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302710</v>
+        <v>122302715</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455835</v>
+        <v>455785</v>
       </c>
       <c r="R10" t="n">
-        <v>6812283</v>
+        <v>6812284</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302581</v>
+        <v>122302539</v>
       </c>
       <c r="B11" t="n">
-        <v>78393</v>
+        <v>79274</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302601</v>
+        <v>122302602</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455785</v>
+        <v>455759</v>
       </c>
       <c r="R12" t="n">
-        <v>6812291</v>
+        <v>6812303</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302712</v>
+        <v>122302709</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455812</v>
+        <v>455848</v>
       </c>
       <c r="R13" t="n">
-        <v>6812304</v>
+        <v>6812261</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302708</v>
+        <v>122302711</v>
       </c>
       <c r="B14" t="n">
         <v>78656</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455856</v>
+        <v>455814</v>
       </c>
       <c r="R14" t="n">
-        <v>6812249</v>
+        <v>6812303</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302704</v>
+        <v>122302581</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455926</v>
+        <v>455818</v>
       </c>
       <c r="R15" t="n">
-        <v>6812197</v>
+        <v>6812302</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302706</v>
+        <v>122302703</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455915</v>
+        <v>455925</v>
       </c>
       <c r="R16" t="n">
-        <v>6812217</v>
+        <v>6812180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302539</v>
+        <v>122302712</v>
       </c>
       <c r="B17" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455818</v>
+        <v>455812</v>
       </c>
       <c r="R17" t="n">
-        <v>6812302</v>
+        <v>6812304</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302699</v>
+        <v>122302551</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>78690</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455957</v>
+        <v>455816</v>
       </c>
       <c r="R18" t="n">
-        <v>6812268</v>
+        <v>6812302</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302705</v>
+        <v>122302714</v>
       </c>
       <c r="B19" t="n">
         <v>78656</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455920</v>
+        <v>455809</v>
       </c>
       <c r="R19" t="n">
-        <v>6812215</v>
+        <v>6812302</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302711</v>
+        <v>122302707</v>
       </c>
       <c r="B20" t="n">
         <v>78656</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455814</v>
+        <v>455876</v>
       </c>
       <c r="R20" t="n">
-        <v>6812303</v>
+        <v>6812238</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302580</v>
+        <v>122302710</v>
       </c>
       <c r="B21" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455866</v>
+        <v>455835</v>
       </c>
       <c r="R21" t="n">
-        <v>6812243</v>
+        <v>6812283</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302551</v>
+        <v>122302582</v>
       </c>
       <c r="B22" t="n">
-        <v>78690</v>
+        <v>78393</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455816</v>
+        <v>455811</v>
       </c>
       <c r="R22" t="n">
-        <v>6812302</v>
+        <v>6812306</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302713</v>
+        <v>122302701</v>
       </c>
       <c r="B23" t="n">
         <v>78656</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455813</v>
+        <v>455958</v>
       </c>
       <c r="R23" t="n">
-        <v>6812305</v>
+        <v>6812214</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302602</v>
+        <v>122302699</v>
       </c>
       <c r="B24" t="n">
         <v>78656</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455759</v>
+        <v>455957</v>
       </c>
       <c r="R24" t="n">
-        <v>6812303</v>
+        <v>6812268</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302701</v>
+        <v>122302601</v>
       </c>
       <c r="B25" t="n">
         <v>78656</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455958</v>
+        <v>455785</v>
       </c>
       <c r="R25" t="n">
-        <v>6812214</v>
+        <v>6812291</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 61224-2024 artfynd.xlsx
+++ b/artfynd/A 61224-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302702</v>
+        <v>122302539</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455951</v>
+        <v>455818</v>
       </c>
       <c r="R2" t="n">
-        <v>6812205</v>
+        <v>6812302</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302713</v>
+        <v>122302715</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455813</v>
+        <v>455785</v>
       </c>
       <c r="R3" t="n">
-        <v>6812305</v>
+        <v>6812284</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302708</v>
+        <v>122302712</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455856</v>
+        <v>455812</v>
       </c>
       <c r="R4" t="n">
-        <v>6812249</v>
+        <v>6812304</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302580</v>
+        <v>122302707</v>
       </c>
       <c r="B5" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455866</v>
+        <v>455876</v>
       </c>
       <c r="R5" t="n">
-        <v>6812243</v>
+        <v>6812238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302706</v>
+        <v>122302582</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455915</v>
+        <v>455811</v>
       </c>
       <c r="R6" t="n">
-        <v>6812217</v>
+        <v>6812306</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302705</v>
+        <v>122302703</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455920</v>
+        <v>455925</v>
       </c>
       <c r="R7" t="n">
-        <v>6812215</v>
+        <v>6812180</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302700</v>
+        <v>122302704</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455975</v>
+        <v>455926</v>
       </c>
       <c r="R8" t="n">
-        <v>6812246</v>
+        <v>6812197</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302704</v>
+        <v>122302710</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455926</v>
+        <v>455835</v>
       </c>
       <c r="R9" t="n">
-        <v>6812197</v>
+        <v>6812283</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302715</v>
+        <v>122302700</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455785</v>
+        <v>455975</v>
       </c>
       <c r="R10" t="n">
-        <v>6812284</v>
+        <v>6812246</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302539</v>
+        <v>122302551</v>
       </c>
       <c r="B11" t="n">
-        <v>79274</v>
+        <v>78690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455818</v>
+        <v>455816</v>
       </c>
       <c r="R11" t="n">
         <v>6812302</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302709</v>
+        <v>122302705</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455848</v>
+        <v>455920</v>
       </c>
       <c r="R13" t="n">
-        <v>6812261</v>
+        <v>6812215</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302711</v>
+        <v>122302706</v>
       </c>
       <c r="B14" t="n">
         <v>78656</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455814</v>
+        <v>455915</v>
       </c>
       <c r="R14" t="n">
-        <v>6812303</v>
+        <v>6812217</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302581</v>
+        <v>122302709</v>
       </c>
       <c r="B15" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455818</v>
+        <v>455848</v>
       </c>
       <c r="R15" t="n">
-        <v>6812302</v>
+        <v>6812261</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302703</v>
+        <v>122302714</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455925</v>
+        <v>455809</v>
       </c>
       <c r="R16" t="n">
-        <v>6812180</v>
+        <v>6812302</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302712</v>
+        <v>122302581</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455812</v>
+        <v>455818</v>
       </c>
       <c r="R17" t="n">
-        <v>6812304</v>
+        <v>6812302</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302551</v>
+        <v>122302711</v>
       </c>
       <c r="B18" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455816</v>
+        <v>455814</v>
       </c>
       <c r="R18" t="n">
-        <v>6812302</v>
+        <v>6812303</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302714</v>
+        <v>122302701</v>
       </c>
       <c r="B19" t="n">
         <v>78656</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455809</v>
+        <v>455958</v>
       </c>
       <c r="R19" t="n">
-        <v>6812302</v>
+        <v>6812214</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302707</v>
+        <v>122302580</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455876</v>
+        <v>455866</v>
       </c>
       <c r="R20" t="n">
-        <v>6812238</v>
+        <v>6812243</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302710</v>
+        <v>122302601</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455835</v>
+        <v>455785</v>
       </c>
       <c r="R21" t="n">
-        <v>6812283</v>
+        <v>6812291</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302582</v>
+        <v>122302699</v>
       </c>
       <c r="B22" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455811</v>
+        <v>455957</v>
       </c>
       <c r="R22" t="n">
-        <v>6812306</v>
+        <v>6812268</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302701</v>
+        <v>122302702</v>
       </c>
       <c r="B23" t="n">
         <v>78656</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455958</v>
+        <v>455951</v>
       </c>
       <c r="R23" t="n">
-        <v>6812214</v>
+        <v>6812205</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302699</v>
+        <v>122302713</v>
       </c>
       <c r="B24" t="n">
         <v>78656</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455957</v>
+        <v>455813</v>
       </c>
       <c r="R24" t="n">
-        <v>6812268</v>
+        <v>6812305</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302601</v>
+        <v>122302708</v>
       </c>
       <c r="B25" t="n">
         <v>78656</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455785</v>
+        <v>455856</v>
       </c>
       <c r="R25" t="n">
-        <v>6812291</v>
+        <v>6812249</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 61224-2024 artfynd.xlsx
+++ b/artfynd/A 61224-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302539</v>
+        <v>122302711</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455818</v>
+        <v>455814</v>
       </c>
       <c r="R2" t="n">
-        <v>6812302</v>
+        <v>6812303</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302715</v>
+        <v>122302581</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455785</v>
+        <v>455818</v>
       </c>
       <c r="R3" t="n">
-        <v>6812284</v>
+        <v>6812302</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302712</v>
+        <v>122302602</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455812</v>
+        <v>455759</v>
       </c>
       <c r="R4" t="n">
-        <v>6812304</v>
+        <v>6812303</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302707</v>
+        <v>122302580</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455876</v>
+        <v>455866</v>
       </c>
       <c r="R5" t="n">
-        <v>6812238</v>
+        <v>6812243</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302582</v>
+        <v>122302707</v>
       </c>
       <c r="B6" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455811</v>
+        <v>455876</v>
       </c>
       <c r="R6" t="n">
-        <v>6812306</v>
+        <v>6812238</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302703</v>
+        <v>122302704</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455925</v>
+        <v>455926</v>
       </c>
       <c r="R7" t="n">
-        <v>6812180</v>
+        <v>6812197</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302704</v>
+        <v>122302551</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>78690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455926</v>
+        <v>455816</v>
       </c>
       <c r="R8" t="n">
-        <v>6812197</v>
+        <v>6812302</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302710</v>
+        <v>122302700</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455835</v>
+        <v>455975</v>
       </c>
       <c r="R9" t="n">
-        <v>6812283</v>
+        <v>6812246</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302700</v>
+        <v>122302713</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455975</v>
+        <v>455813</v>
       </c>
       <c r="R10" t="n">
-        <v>6812246</v>
+        <v>6812305</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302551</v>
+        <v>122302703</v>
       </c>
       <c r="B11" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455816</v>
+        <v>455925</v>
       </c>
       <c r="R11" t="n">
-        <v>6812302</v>
+        <v>6812180</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302602</v>
+        <v>122302705</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455759</v>
+        <v>455920</v>
       </c>
       <c r="R12" t="n">
-        <v>6812303</v>
+        <v>6812215</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302705</v>
+        <v>122302601</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455920</v>
+        <v>455785</v>
       </c>
       <c r="R13" t="n">
-        <v>6812215</v>
+        <v>6812291</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302706</v>
+        <v>122302539</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455915</v>
+        <v>455818</v>
       </c>
       <c r="R14" t="n">
-        <v>6812217</v>
+        <v>6812302</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302709</v>
+        <v>122302582</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455848</v>
+        <v>455811</v>
       </c>
       <c r="R15" t="n">
-        <v>6812261</v>
+        <v>6812306</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302714</v>
+        <v>122302702</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455809</v>
+        <v>455951</v>
       </c>
       <c r="R16" t="n">
-        <v>6812302</v>
+        <v>6812205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302581</v>
+        <v>122302701</v>
       </c>
       <c r="B17" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455818</v>
+        <v>455958</v>
       </c>
       <c r="R17" t="n">
-        <v>6812302</v>
+        <v>6812214</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302711</v>
+        <v>122302699</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455814</v>
+        <v>455957</v>
       </c>
       <c r="R18" t="n">
-        <v>6812303</v>
+        <v>6812268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302701</v>
+        <v>122302706</v>
       </c>
       <c r="B19" t="n">
         <v>78656</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455958</v>
+        <v>455915</v>
       </c>
       <c r="R19" t="n">
-        <v>6812214</v>
+        <v>6812217</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302580</v>
+        <v>122302712</v>
       </c>
       <c r="B20" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455866</v>
+        <v>455812</v>
       </c>
       <c r="R20" t="n">
-        <v>6812243</v>
+        <v>6812304</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302601</v>
+        <v>122302710</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455785</v>
+        <v>455835</v>
       </c>
       <c r="R21" t="n">
-        <v>6812291</v>
+        <v>6812283</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302699</v>
+        <v>122302714</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455957</v>
+        <v>455809</v>
       </c>
       <c r="R22" t="n">
-        <v>6812268</v>
+        <v>6812302</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302702</v>
+        <v>122302715</v>
       </c>
       <c r="B23" t="n">
         <v>78656</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455951</v>
+        <v>455785</v>
       </c>
       <c r="R23" t="n">
-        <v>6812205</v>
+        <v>6812284</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302713</v>
+        <v>122302709</v>
       </c>
       <c r="B24" t="n">
         <v>78656</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455813</v>
+        <v>455848</v>
       </c>
       <c r="R24" t="n">
-        <v>6812305</v>
+        <v>6812261</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 61224-2024 artfynd.xlsx
+++ b/artfynd/A 61224-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302711</v>
+        <v>122302713</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455814</v>
+        <v>455813</v>
       </c>
       <c r="R2" t="n">
-        <v>6812303</v>
+        <v>6812305</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302581</v>
+        <v>122302702</v>
       </c>
       <c r="B3" t="n">
-        <v>78393</v>
+        <v>78657</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455818</v>
+        <v>455951</v>
       </c>
       <c r="R3" t="n">
-        <v>6812302</v>
+        <v>6812205</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302602</v>
+        <v>122302582</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>78394</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455759</v>
+        <v>455811</v>
       </c>
       <c r="R4" t="n">
-        <v>6812303</v>
+        <v>6812306</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302580</v>
+        <v>122302551</v>
       </c>
       <c r="B5" t="n">
-        <v>78393</v>
+        <v>78691</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455866</v>
+        <v>455816</v>
       </c>
       <c r="R5" t="n">
-        <v>6812243</v>
+        <v>6812302</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302707</v>
+        <v>122302715</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455876</v>
+        <v>455785</v>
       </c>
       <c r="R6" t="n">
-        <v>6812238</v>
+        <v>6812284</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302704</v>
+        <v>122302581</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>78394</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455926</v>
+        <v>455818</v>
       </c>
       <c r="R7" t="n">
-        <v>6812197</v>
+        <v>6812302</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302551</v>
+        <v>122302539</v>
       </c>
       <c r="B8" t="n">
-        <v>78690</v>
+        <v>79275</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455816</v>
+        <v>455818</v>
       </c>
       <c r="R8" t="n">
         <v>6812302</v>
@@ -1392,7 +1392,7 @@
         <v>122302700</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302713</v>
+        <v>122302602</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455813</v>
+        <v>455759</v>
       </c>
       <c r="R10" t="n">
-        <v>6812305</v>
+        <v>6812303</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302703</v>
+        <v>122302704</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455925</v>
+        <v>455926</v>
       </c>
       <c r="R11" t="n">
-        <v>6812180</v>
+        <v>6812197</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302705</v>
+        <v>122302708</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455920</v>
+        <v>455856</v>
       </c>
       <c r="R12" t="n">
-        <v>6812215</v>
+        <v>6812249</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302601</v>
+        <v>122302709</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455785</v>
+        <v>455848</v>
       </c>
       <c r="R13" t="n">
-        <v>6812291</v>
+        <v>6812261</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302539</v>
+        <v>122302580</v>
       </c>
       <c r="B14" t="n">
-        <v>79274</v>
+        <v>78394</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455818</v>
+        <v>455866</v>
       </c>
       <c r="R14" t="n">
-        <v>6812302</v>
+        <v>6812243</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302582</v>
+        <v>122302714</v>
       </c>
       <c r="B15" t="n">
-        <v>78393</v>
+        <v>78657</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455811</v>
+        <v>455809</v>
       </c>
       <c r="R15" t="n">
-        <v>6812306</v>
+        <v>6812302</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302702</v>
+        <v>122302699</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455951</v>
+        <v>455957</v>
       </c>
       <c r="R16" t="n">
-        <v>6812205</v>
+        <v>6812268</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302701</v>
+        <v>122302710</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455958</v>
+        <v>455835</v>
       </c>
       <c r="R17" t="n">
-        <v>6812214</v>
+        <v>6812283</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302699</v>
+        <v>122302707</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455957</v>
+        <v>455876</v>
       </c>
       <c r="R18" t="n">
-        <v>6812268</v>
+        <v>6812238</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302706</v>
+        <v>122302712</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455915</v>
+        <v>455812</v>
       </c>
       <c r="R19" t="n">
-        <v>6812217</v>
+        <v>6812304</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302712</v>
+        <v>122302706</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455812</v>
+        <v>455915</v>
       </c>
       <c r="R20" t="n">
-        <v>6812304</v>
+        <v>6812217</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302710</v>
+        <v>122302711</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455835</v>
+        <v>455814</v>
       </c>
       <c r="R21" t="n">
-        <v>6812283</v>
+        <v>6812303</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302714</v>
+        <v>122302701</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455809</v>
+        <v>455958</v>
       </c>
       <c r="R22" t="n">
-        <v>6812302</v>
+        <v>6812214</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302715</v>
+        <v>122302703</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455785</v>
+        <v>455925</v>
       </c>
       <c r="R23" t="n">
-        <v>6812284</v>
+        <v>6812180</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302709</v>
+        <v>122302705</v>
       </c>
       <c r="B24" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455848</v>
+        <v>455920</v>
       </c>
       <c r="R24" t="n">
-        <v>6812261</v>
+        <v>6812215</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302708</v>
+        <v>122302601</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455856</v>
+        <v>455785</v>
       </c>
       <c r="R25" t="n">
-        <v>6812249</v>
+        <v>6812291</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 61224-2024 artfynd.xlsx
+++ b/artfynd/A 61224-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302713</v>
+        <v>122302703</v>
       </c>
       <c r="B2" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455813</v>
+        <v>455925</v>
       </c>
       <c r="R2" t="n">
-        <v>6812305</v>
+        <v>6812180</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302702</v>
+        <v>122302707</v>
       </c>
       <c r="B3" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455951</v>
+        <v>455876</v>
       </c>
       <c r="R3" t="n">
-        <v>6812205</v>
+        <v>6812238</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302582</v>
+        <v>122302710</v>
       </c>
       <c r="B4" t="n">
-        <v>78394</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455811</v>
+        <v>455835</v>
       </c>
       <c r="R4" t="n">
-        <v>6812306</v>
+        <v>6812283</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>122302551</v>
       </c>
       <c r="B5" t="n">
-        <v>78691</v>
+        <v>78694</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302715</v>
+        <v>122302699</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455785</v>
+        <v>455957</v>
       </c>
       <c r="R6" t="n">
-        <v>6812284</v>
+        <v>6812268</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302581</v>
+        <v>122302701</v>
       </c>
       <c r="B7" t="n">
-        <v>78394</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455818</v>
+        <v>455958</v>
       </c>
       <c r="R7" t="n">
-        <v>6812302</v>
+        <v>6812214</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302539</v>
+        <v>122302704</v>
       </c>
       <c r="B8" t="n">
-        <v>79275</v>
+        <v>78660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455818</v>
+        <v>455926</v>
       </c>
       <c r="R8" t="n">
-        <v>6812302</v>
+        <v>6812197</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302700</v>
+        <v>122302711</v>
       </c>
       <c r="B9" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455975</v>
+        <v>455814</v>
       </c>
       <c r="R9" t="n">
-        <v>6812246</v>
+        <v>6812303</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
         <v>122302602</v>
       </c>
       <c r="B10" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302704</v>
+        <v>122302539</v>
       </c>
       <c r="B11" t="n">
-        <v>78657</v>
+        <v>79278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455926</v>
+        <v>455818</v>
       </c>
       <c r="R11" t="n">
-        <v>6812197</v>
+        <v>6812302</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302708</v>
+        <v>122302709</v>
       </c>
       <c r="B12" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455856</v>
+        <v>455848</v>
       </c>
       <c r="R12" t="n">
-        <v>6812249</v>
+        <v>6812261</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302709</v>
+        <v>122302712</v>
       </c>
       <c r="B13" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455848</v>
+        <v>455812</v>
       </c>
       <c r="R13" t="n">
-        <v>6812261</v>
+        <v>6812304</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302580</v>
+        <v>122302705</v>
       </c>
       <c r="B14" t="n">
-        <v>78394</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455866</v>
+        <v>455920</v>
       </c>
       <c r="R14" t="n">
-        <v>6812243</v>
+        <v>6812215</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302714</v>
+        <v>122302702</v>
       </c>
       <c r="B15" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455809</v>
+        <v>455951</v>
       </c>
       <c r="R15" t="n">
-        <v>6812302</v>
+        <v>6812205</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302699</v>
+        <v>122302582</v>
       </c>
       <c r="B16" t="n">
-        <v>78657</v>
+        <v>78397</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455957</v>
+        <v>455811</v>
       </c>
       <c r="R16" t="n">
-        <v>6812268</v>
+        <v>6812306</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302710</v>
+        <v>122302714</v>
       </c>
       <c r="B17" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455835</v>
+        <v>455809</v>
       </c>
       <c r="R17" t="n">
-        <v>6812283</v>
+        <v>6812302</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302707</v>
+        <v>122302700</v>
       </c>
       <c r="B18" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455876</v>
+        <v>455975</v>
       </c>
       <c r="R18" t="n">
-        <v>6812238</v>
+        <v>6812246</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302712</v>
+        <v>122302706</v>
       </c>
       <c r="B19" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455812</v>
+        <v>455915</v>
       </c>
       <c r="R19" t="n">
-        <v>6812304</v>
+        <v>6812217</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302706</v>
+        <v>122302713</v>
       </c>
       <c r="B20" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455915</v>
+        <v>455813</v>
       </c>
       <c r="R20" t="n">
-        <v>6812217</v>
+        <v>6812305</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302711</v>
+        <v>122302708</v>
       </c>
       <c r="B21" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455814</v>
+        <v>455856</v>
       </c>
       <c r="R21" t="n">
-        <v>6812303</v>
+        <v>6812249</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302701</v>
+        <v>122302715</v>
       </c>
       <c r="B22" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455958</v>
+        <v>455785</v>
       </c>
       <c r="R22" t="n">
-        <v>6812214</v>
+        <v>6812284</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302703</v>
+        <v>122302581</v>
       </c>
       <c r="B23" t="n">
-        <v>78657</v>
+        <v>78397</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455925</v>
+        <v>455818</v>
       </c>
       <c r="R23" t="n">
-        <v>6812180</v>
+        <v>6812302</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302705</v>
+        <v>122302601</v>
       </c>
       <c r="B24" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455920</v>
+        <v>455785</v>
       </c>
       <c r="R24" t="n">
-        <v>6812215</v>
+        <v>6812291</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302601</v>
+        <v>122302580</v>
       </c>
       <c r="B25" t="n">
-        <v>78657</v>
+        <v>78397</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455785</v>
+        <v>455866</v>
       </c>
       <c r="R25" t="n">
-        <v>6812291</v>
+        <v>6812243</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 61224-2024 artfynd.xlsx
+++ b/artfynd/A 61224-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302703</v>
+        <v>122302706</v>
       </c>
       <c r="B2" t="n">
         <v>78660</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455925</v>
+        <v>455915</v>
       </c>
       <c r="R2" t="n">
-        <v>6812180</v>
+        <v>6812217</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302707</v>
+        <v>122302700</v>
       </c>
       <c r="B3" t="n">
         <v>78660</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455876</v>
+        <v>455975</v>
       </c>
       <c r="R3" t="n">
-        <v>6812238</v>
+        <v>6812246</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302710</v>
+        <v>122302712</v>
       </c>
       <c r="B4" t="n">
         <v>78660</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455835</v>
+        <v>455812</v>
       </c>
       <c r="R4" t="n">
-        <v>6812283</v>
+        <v>6812304</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302551</v>
+        <v>122302705</v>
       </c>
       <c r="B5" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455816</v>
+        <v>455920</v>
       </c>
       <c r="R5" t="n">
-        <v>6812302</v>
+        <v>6812215</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302699</v>
+        <v>122302714</v>
       </c>
       <c r="B6" t="n">
         <v>78660</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455957</v>
+        <v>455809</v>
       </c>
       <c r="R6" t="n">
-        <v>6812268</v>
+        <v>6812302</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302701</v>
+        <v>122302707</v>
       </c>
       <c r="B7" t="n">
         <v>78660</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455958</v>
+        <v>455876</v>
       </c>
       <c r="R7" t="n">
-        <v>6812214</v>
+        <v>6812238</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302704</v>
+        <v>122302601</v>
       </c>
       <c r="B8" t="n">
         <v>78660</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455926</v>
+        <v>455785</v>
       </c>
       <c r="R8" t="n">
-        <v>6812197</v>
+        <v>6812291</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302711</v>
+        <v>122302703</v>
       </c>
       <c r="B9" t="n">
         <v>78660</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455814</v>
+        <v>455925</v>
       </c>
       <c r="R9" t="n">
-        <v>6812303</v>
+        <v>6812180</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302602</v>
+        <v>122302539</v>
       </c>
       <c r="B10" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455759</v>
+        <v>455818</v>
       </c>
       <c r="R10" t="n">
-        <v>6812303</v>
+        <v>6812302</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302539</v>
+        <v>122302709</v>
       </c>
       <c r="B11" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455818</v>
+        <v>455848</v>
       </c>
       <c r="R11" t="n">
-        <v>6812302</v>
+        <v>6812261</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302709</v>
+        <v>122302710</v>
       </c>
       <c r="B12" t="n">
         <v>78660</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455848</v>
+        <v>455835</v>
       </c>
       <c r="R12" t="n">
-        <v>6812261</v>
+        <v>6812283</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302712</v>
+        <v>122302582</v>
       </c>
       <c r="B13" t="n">
-        <v>78660</v>
+        <v>78397</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455812</v>
+        <v>455811</v>
       </c>
       <c r="R13" t="n">
-        <v>6812304</v>
+        <v>6812306</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302705</v>
+        <v>122302702</v>
       </c>
       <c r="B14" t="n">
         <v>78660</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455920</v>
+        <v>455951</v>
       </c>
       <c r="R14" t="n">
-        <v>6812215</v>
+        <v>6812205</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302702</v>
+        <v>122302704</v>
       </c>
       <c r="B15" t="n">
         <v>78660</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455951</v>
+        <v>455926</v>
       </c>
       <c r="R15" t="n">
-        <v>6812205</v>
+        <v>6812197</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302582</v>
+        <v>122302701</v>
       </c>
       <c r="B16" t="n">
-        <v>78397</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455811</v>
+        <v>455958</v>
       </c>
       <c r="R16" t="n">
-        <v>6812306</v>
+        <v>6812214</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302714</v>
+        <v>122302713</v>
       </c>
       <c r="B17" t="n">
         <v>78660</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455809</v>
+        <v>455813</v>
       </c>
       <c r="R17" t="n">
-        <v>6812302</v>
+        <v>6812305</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302700</v>
+        <v>122302708</v>
       </c>
       <c r="B18" t="n">
         <v>78660</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455975</v>
+        <v>455856</v>
       </c>
       <c r="R18" t="n">
-        <v>6812246</v>
+        <v>6812249</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302706</v>
+        <v>122302711</v>
       </c>
       <c r="B19" t="n">
         <v>78660</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455915</v>
+        <v>455814</v>
       </c>
       <c r="R19" t="n">
-        <v>6812217</v>
+        <v>6812303</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302713</v>
+        <v>122302580</v>
       </c>
       <c r="B20" t="n">
-        <v>78660</v>
+        <v>78397</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455813</v>
+        <v>455866</v>
       </c>
       <c r="R20" t="n">
-        <v>6812305</v>
+        <v>6812243</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302708</v>
+        <v>122302715</v>
       </c>
       <c r="B21" t="n">
         <v>78660</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455856</v>
+        <v>455785</v>
       </c>
       <c r="R21" t="n">
-        <v>6812249</v>
+        <v>6812284</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302715</v>
+        <v>122302699</v>
       </c>
       <c r="B22" t="n">
         <v>78660</v>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455785</v>
+        <v>455957</v>
       </c>
       <c r="R22" t="n">
-        <v>6812284</v>
+        <v>6812268</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302581</v>
+        <v>122302551</v>
       </c>
       <c r="B23" t="n">
-        <v>78397</v>
+        <v>78694</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455818</v>
+        <v>455816</v>
       </c>
       <c r="R23" t="n">
         <v>6812302</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302601</v>
+        <v>122302602</v>
       </c>
       <c r="B24" t="n">
         <v>78660</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455785</v>
+        <v>455759</v>
       </c>
       <c r="R24" t="n">
-        <v>6812291</v>
+        <v>6812303</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302580</v>
+        <v>122302581</v>
       </c>
       <c r="B25" t="n">
         <v>78397</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455866</v>
+        <v>455818</v>
       </c>
       <c r="R25" t="n">
-        <v>6812243</v>
+        <v>6812302</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
